--- a/docs/StructureDefinition-BRCID10Avaliado-1.0.xlsx
+++ b/docs/StructureDefinition-BRCID10Avaliado-1.0.xlsx
@@ -2099,15 +2099,15 @@
   <dimension ref="A1:AP99"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="68.29296875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="42.765625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.4921875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="37.5859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.9296875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.47265625" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.87890625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.2734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.7265625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="65.125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.78125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="16.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="35.84375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.65234375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65234375" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.1796875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2118,28 +2118,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="36.22265625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.4609375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="15.86328125" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.203125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="91.51171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="76.1328125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.52734375" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="38.34375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.06640625" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.421875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="32.73046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.28515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.6875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="34.54296875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.7421875" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.12890625" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.40625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="15.85546875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="87.265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="72.59765625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.2734375" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.1171875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.56640625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.3671875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.84375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="31.2109375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.85546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.23828125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.359375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.13671875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="63.484375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="204.25" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="32.4453125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="37.3671875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="60.5390625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="194.7734375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="30.9375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="35.6328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7212,7 +7212,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-BRCID10Avaliado-1.0.xlsx
+++ b/docs/StructureDefinition-BRCID10Avaliado-1.0.xlsx
@@ -376,7 +376,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -840,7 +840,7 @@
     <t>Coding of the severity with a terminology is preferred, where possible.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-severity</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-severity|4.0.1</t>
   </si>
   <si>
     <t>&lt; 272141005 |Severities|</t>
@@ -955,7 +955,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 442083009  |Anatomical or acquired body structure|</t>
@@ -1193,7 +1193,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1271,7 +1271,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1356,7 +1356,7 @@
     <t>Condition.subject.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1396,7 +1396,7 @@
     <t>Condition.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1496,7 +1496,7 @@
     <t>Condition.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1585,7 +1585,7 @@
     <t>Codes describing condition stages (e.g. Cancer stages).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-stage</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-stage|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">con-1
@@ -1598,7 +1598,7 @@
     <t>Condition.stage.assessment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ClinicalImpression|DiagnosticReport|Observation)
+    <t xml:space="preserve">Reference(ClinicalImpression|4.0.1|DiagnosticReport|4.0.1|Observation|4.0.1)
 </t>
   </si>
   <si>
@@ -1623,7 +1623,7 @@
     <t>Codes describing the kind of condition staging (e.g. clinical or pathological).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-stage-type</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-stage-type|4.0.1</t>
   </si>
   <si>
     <t>./inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="stage type"]</t>
@@ -1669,7 +1669,7 @@
     <t>Codes that describe the manifestation or symptoms of a condition.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom</t>
+    <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">con-2
@@ -1688,7 +1688,7 @@
     <t>Condition.evidence.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1729,7 +1729,7 @@
     <t>Condition.note.author[x]</t>
   </si>
   <si>
-    <t>Reference(Practitioner|Patient|RelatedPerson|Organization)
+    <t>Reference(Practitioner|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 string</t>
   </si>
   <si>

--- a/docs/StructureDefinition-BRCID10Avaliado-1.0.xlsx
+++ b/docs/StructureDefinition-BRCID10Avaliado-1.0.xlsx
@@ -2270,7 +2270,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -3470,7 +3470,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>157</v>
       </c>
@@ -3828,7 +3828,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>183</v>
       </c>
@@ -5274,7 +5274,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>270</v>
       </c>
@@ -6838,7 +6838,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>303</v>
       </c>
@@ -7194,7 +7194,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>317</v>
       </c>
@@ -7550,7 +7550,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>327</v>
       </c>
@@ -8146,7 +8146,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>344</v>
       </c>
@@ -8742,7 +8742,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>351</v>
       </c>
@@ -13280,7 +13280,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
         <v>538</v>
       </c>
@@ -13874,7 +13874,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="99" hidden="true">
+    <row r="99">
       <c r="A99" t="s" s="2">
         <v>559</v>
       </c>
@@ -13994,12 +13994,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP99">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/docs/StructureDefinition-BRCID10Avaliado-1.0.xlsx
+++ b/docs/StructureDefinition-BRCID10Avaliado-1.0.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br)</t>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
